--- a/02-Execucao/03-Execucao_Procedimentos/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/tabelas_consolidadas_auditoria.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5776" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5792" uniqueCount="176">
   <si>
     <t>1. Estrutura de TIC insuficiente para coordenar, gerir e sustentar a tecnologia da informação.</t>
   </si>
@@ -412,7 +412,7 @@
     <t>[Recomendação] designe formalmente equipe responsável pelo planejamento das contratações de TIC, atentando-se, minimamente, em assegurar a participação da área requisitante, da área técnica de TIC e das demais áreas necessárias, com definição das responsabilidades de seus integrantes</t>
   </si>
   <si>
-    <t>[Recomendação] estabeleça a submissão das contratações de TIC à análise prévia e à aprovação técnica da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente</t>
+    <t>[Recomendação] estabeleça a submissão das contratações de TIC à análise prévia e à aprovação técnica da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente, facultando a adoção de fluxos simplificados ou a dispensa de parecer detalhado para contratações diretas por dispensa em razão do valor (baixo valor) ou de baixa complexidade técnica, mediante critérios objetivos ou catálogos de soluções padronizadas</t>
   </si>
   <si>
     <t>[Recomendação] estabeleça e execute rotina periódica de acompanhamento, revisão e atualização do plano de TIC, atentando-se, minimamente, em registrar a execução das iniciativas, as pendências, as reprogramações e as deliberações adotadas</t>
@@ -3899,6 +3899,9 @@
       <c r="C8" t="s">
         <v>121</v>
       </c>
+      <c r="D8" t="s">
+        <v>121</v>
+      </c>
       <c r="E8" t="s">
         <v>121</v>
       </c>
@@ -3914,6 +3917,12 @@
       <c r="I8" t="s">
         <v>121</v>
       </c>
+      <c r="J8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" t="s">
+        <v>121</v>
+      </c>
       <c r="L8" t="s">
         <v>121</v>
       </c>
@@ -3924,6 +3933,9 @@
         <v>121</v>
       </c>
       <c r="O8" t="s">
+        <v>121</v>
+      </c>
+      <c r="P8" t="s">
         <v>121</v>
       </c>
       <c r="Q8" t="s">
@@ -4669,6 +4681,9 @@
       <c r="C21" t="s">
         <v>121</v>
       </c>
+      <c r="D21" t="s">
+        <v>121</v>
+      </c>
       <c r="E21" t="s">
         <v>121</v>
       </c>
@@ -4684,6 +4699,12 @@
       <c r="I21" t="s">
         <v>121</v>
       </c>
+      <c r="J21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" t="s">
+        <v>121</v>
+      </c>
       <c r="L21" t="s">
         <v>121</v>
       </c>
@@ -4694,6 +4715,9 @@
         <v>121</v>
       </c>
       <c r="O21" t="s">
+        <v>121</v>
+      </c>
+      <c r="P21" t="s">
         <v>121</v>
       </c>
       <c r="Q21" t="s">
@@ -11498,6 +11522,9 @@
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
       <c r="C8" t="s">
         <v>121</v>
       </c>
@@ -11534,6 +11561,9 @@
       <c r="N8" t="s">
         <v>121</v>
       </c>
+      <c r="O8" t="s">
+        <v>121</v>
+      </c>
       <c r="P8" t="s">
         <v>121</v>
       </c>
@@ -11561,7 +11591,13 @@
       <c r="X8" t="s">
         <v>121</v>
       </c>
+      <c r="Y8" t="s">
+        <v>121</v>
+      </c>
       <c r="Z8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA8" t="s">
         <v>121</v>
       </c>
     </row>
@@ -12268,6 +12304,9 @@
       <c r="A21" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="B21" t="s">
+        <v>121</v>
+      </c>
       <c r="C21" t="s">
         <v>121</v>
       </c>
@@ -12304,6 +12343,9 @@
       <c r="N21" t="s">
         <v>121</v>
       </c>
+      <c r="O21" t="s">
+        <v>121</v>
+      </c>
       <c r="P21" t="s">
         <v>121</v>
       </c>
@@ -12331,7 +12373,13 @@
       <c r="X21" t="s">
         <v>121</v>
       </c>
+      <c r="Y21" t="s">
+        <v>121</v>
+      </c>
       <c r="Z21" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA21" t="s">
         <v>121</v>
       </c>
     </row>
@@ -18615,7 +18663,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -18626,7 +18674,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -18637,7 +18685,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -18648,7 +18696,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -18659,29 +18707,29 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -18692,7 +18740,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -18703,7 +18751,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -18714,7 +18762,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -18725,7 +18773,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -18736,7 +18784,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -18747,7 +18795,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -18758,7 +18806,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -18769,7 +18817,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -18780,7 +18828,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -18791,7 +18839,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -18802,7 +18850,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -18813,7 +18861,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -18824,29 +18872,29 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -18857,7 +18905,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -18868,7 +18916,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -18879,7 +18927,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -18890,7 +18938,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -18901,29 +18949,29 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -18934,7 +18982,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -18945,7 +18993,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B32">
         <v>6</v>
@@ -18956,7 +19004,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B33">
         <v>6</v>
@@ -18967,7 +19015,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -18978,7 +19026,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -18989,7 +19037,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -19000,7 +19048,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -19011,7 +19059,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -19022,7 +19070,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -19033,24 +19081,24 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="B40">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:3">

--- a/02-Execucao/03-Execucao_Procedimentos/tabelas_consolidadas_auditoria.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/tabelas_consolidadas_auditoria.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5792" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5782" uniqueCount="176">
   <si>
     <t>1. Estrutura de TIC insuficiente para coordenar, gerir e sustentar a tecnologia da informação.</t>
   </si>
@@ -551,16 +551,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -576,7 +568,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -584,30 +576,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,30 +880,30 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -952,7 +926,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -975,7 +949,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
@@ -998,7 +972,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -1021,7 +995,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -1044,7 +1018,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
@@ -1064,7 +1038,7 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
@@ -1087,7 +1061,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
@@ -1110,7 +1084,7 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
@@ -1127,7 +1101,7 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
@@ -1138,7 +1112,7 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
@@ -1158,7 +1132,7 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
@@ -1178,7 +1152,7 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
@@ -1198,7 +1172,7 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
@@ -1221,7 +1195,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
@@ -1238,7 +1212,7 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
@@ -1261,7 +1235,7 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
@@ -1284,7 +1258,7 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
@@ -1304,7 +1278,7 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="C20" t="s">
@@ -1324,7 +1298,7 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
@@ -1347,7 +1321,7 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
@@ -1370,7 +1344,7 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
@@ -1390,7 +1364,7 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" t="s">
@@ -1413,7 +1387,7 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25" t="s">
@@ -1436,7 +1410,7 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26" t="s">
@@ -1459,7 +1433,7 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27" t="s">
@@ -1482,7 +1456,7 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28" t="s">
@@ -1505,7 +1479,7 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
@@ -1528,7 +1502,7 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
@@ -1551,7 +1525,7 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="C31" t="s">
@@ -1571,7 +1545,7 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32" t="s">
@@ -1591,7 +1565,7 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
@@ -1614,7 +1588,7 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
@@ -1634,7 +1608,7 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35" t="s">
@@ -1657,7 +1631,7 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="C36" t="s">
@@ -1677,7 +1651,7 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="C37" t="s">
@@ -1697,7 +1671,7 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38" t="s">
@@ -1720,7 +1694,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39" t="s">
@@ -1743,7 +1717,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40" t="s">
@@ -1766,7 +1740,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41" t="s">
@@ -1789,7 +1763,7 @@
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="E42" t="s">
@@ -1803,7 +1777,7 @@
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="C43" t="s">
@@ -1823,7 +1797,7 @@
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
@@ -1837,7 +1811,7 @@
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45" t="s">
@@ -1851,7 +1825,7 @@
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46" t="s">
@@ -1874,7 +1848,7 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="C47" t="s">
@@ -1888,7 +1862,7 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="C48" t="s">
@@ -1905,7 +1879,7 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49" t="s">
@@ -1928,7 +1902,7 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50" t="s">
@@ -1945,7 +1919,7 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="B51" t="s">
@@ -1968,7 +1942,7 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="B52" t="s">
@@ -1991,7 +1965,7 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53" t="s">
@@ -2014,7 +1988,7 @@
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54" t="s">
@@ -2034,7 +2008,7 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55" t="s">
@@ -2057,7 +2031,7 @@
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>61</v>
       </c>
       <c r="B56" t="s">
@@ -2077,7 +2051,7 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>62</v>
       </c>
       <c r="B57" t="s">
@@ -2100,7 +2074,7 @@
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58" t="s">
@@ -2123,7 +2097,7 @@
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="B59" t="s">
@@ -2146,7 +2120,7 @@
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60" t="s">
@@ -2169,7 +2143,7 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>66</v>
       </c>
       <c r="B61" t="s">
@@ -2192,7 +2166,7 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62" t="s">
@@ -2215,7 +2189,7 @@
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="C63" t="s">
@@ -2229,7 +2203,7 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>69</v>
       </c>
       <c r="B64" t="s">
@@ -2252,7 +2226,7 @@
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65" t="s">
@@ -2275,7 +2249,7 @@
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>71</v>
       </c>
       <c r="B66" t="s">
@@ -2298,7 +2272,7 @@
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>72</v>
       </c>
       <c r="B67" t="s">
@@ -2321,7 +2295,7 @@
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>73</v>
       </c>
       <c r="B68" t="s">
@@ -2338,7 +2312,7 @@
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>74</v>
       </c>
       <c r="B69" t="s">
@@ -2361,7 +2335,7 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>75</v>
       </c>
       <c r="B70" t="s">
@@ -2384,7 +2358,7 @@
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>76</v>
       </c>
       <c r="B71" t="s">
@@ -2407,7 +2381,7 @@
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>77</v>
       </c>
       <c r="B72" t="s">
@@ -2424,7 +2398,7 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>78</v>
       </c>
       <c r="B73" t="s">
@@ -2447,7 +2421,7 @@
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>79</v>
       </c>
       <c r="B74" t="s">
@@ -2470,7 +2444,7 @@
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>80</v>
       </c>
       <c r="C75" t="s">
@@ -2490,7 +2464,7 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>81</v>
       </c>
       <c r="B76" t="s">
@@ -2513,7 +2487,7 @@
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>82</v>
       </c>
       <c r="B77" t="s">
@@ -2536,7 +2510,7 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>83</v>
       </c>
       <c r="D78" t="s">
@@ -2550,7 +2524,7 @@
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>84</v>
       </c>
       <c r="B79" t="s">
@@ -2573,7 +2547,7 @@
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>85</v>
       </c>
       <c r="C80" t="s">
@@ -2593,7 +2567,7 @@
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>86</v>
       </c>
       <c r="B81" t="s">
@@ -2616,7 +2590,7 @@
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>87</v>
       </c>
       <c r="B82" t="s">
@@ -2639,7 +2613,7 @@
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>88</v>
       </c>
       <c r="B83" t="s">
@@ -2662,7 +2636,7 @@
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>89</v>
       </c>
       <c r="B84" t="s">
@@ -2685,7 +2659,7 @@
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>90</v>
       </c>
       <c r="B85" t="s">
@@ -2708,7 +2682,7 @@
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>91</v>
       </c>
       <c r="C86" t="s">
@@ -2728,7 +2702,7 @@
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>92</v>
       </c>
       <c r="B87" t="s">
@@ -2751,7 +2725,7 @@
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>93</v>
       </c>
       <c r="B88" t="s">
@@ -2774,7 +2748,7 @@
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>94</v>
       </c>
       <c r="B89" t="s">
@@ -2797,7 +2771,7 @@
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>95</v>
       </c>
       <c r="B90" t="s">
@@ -2820,7 +2794,7 @@
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>96</v>
       </c>
       <c r="B91" t="s">
@@ -2843,7 +2817,7 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>97</v>
       </c>
       <c r="C92" t="s">
@@ -2863,7 +2837,7 @@
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>98</v>
       </c>
       <c r="B93" t="s">
@@ -2886,7 +2860,7 @@
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>99</v>
       </c>
       <c r="B94" t="s">
@@ -2909,7 +2883,7 @@
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>100</v>
       </c>
       <c r="B95" t="s">
@@ -2932,7 +2906,7 @@
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>101</v>
       </c>
       <c r="B96" t="s">
@@ -2955,7 +2929,7 @@
       </c>
     </row>
     <row r="97" spans="1:7">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>102</v>
       </c>
       <c r="B97" t="s">
@@ -2978,7 +2952,7 @@
       </c>
     </row>
     <row r="98" spans="1:7">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>103</v>
       </c>
       <c r="B98" t="s">
@@ -3001,7 +2975,7 @@
       </c>
     </row>
     <row r="99" spans="1:7">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>104</v>
       </c>
       <c r="B99" t="s">
@@ -3024,7 +2998,7 @@
       </c>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>105</v>
       </c>
       <c r="B100" t="s">
@@ -3047,7 +3021,7 @@
       </c>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>106</v>
       </c>
       <c r="B101" t="s">
@@ -3070,7 +3044,7 @@
       </c>
     </row>
     <row r="102" spans="1:7">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>107</v>
       </c>
       <c r="B102" t="s">
@@ -3093,7 +3067,7 @@
       </c>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>108</v>
       </c>
       <c r="B103" t="s">
@@ -3116,7 +3090,7 @@
       </c>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>109</v>
       </c>
       <c r="B104" t="s">
@@ -3139,7 +3113,7 @@
       </c>
     </row>
     <row r="105" spans="1:7">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>110</v>
       </c>
       <c r="B105" t="s">
@@ -3162,7 +3136,7 @@
       </c>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>111</v>
       </c>
       <c r="B106" t="s">
@@ -3185,7 +3159,7 @@
       </c>
     </row>
     <row r="107" spans="1:7">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>112</v>
       </c>
       <c r="C107" t="s">
@@ -3205,7 +3179,7 @@
       </c>
     </row>
     <row r="108" spans="1:7">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>113</v>
       </c>
       <c r="B108" t="s">
@@ -3228,7 +3202,7 @@
       </c>
     </row>
     <row r="109" spans="1:7">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>114</v>
       </c>
       <c r="B109" t="s">
@@ -3251,7 +3225,7 @@
       </c>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>115</v>
       </c>
       <c r="B110" t="s">
@@ -3274,7 +3248,7 @@
       </c>
     </row>
     <row r="111" spans="1:7">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>116</v>
       </c>
       <c r="B111" t="s">
@@ -3297,7 +3271,7 @@
       </c>
     </row>
     <row r="112" spans="1:7">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>117</v>
       </c>
       <c r="B112" t="s">
@@ -3320,7 +3294,7 @@
       </c>
     </row>
     <row r="113" spans="1:7">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>118</v>
       </c>
       <c r="B113" t="s">
@@ -3343,7 +3317,7 @@
       </c>
     </row>
     <row r="114" spans="1:7">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>119</v>
       </c>
       <c r="B114" t="s">
@@ -3363,7 +3337,7 @@
       </c>
     </row>
     <row r="115" spans="1:7">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>120</v>
       </c>
       <c r="B115" t="s">
@@ -3396,90 +3370,90 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>125</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>126</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>127</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>128</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>131</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>132</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>133</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>134</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>135</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>136</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>137</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>138</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>139</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>140</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>141</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>142</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>143</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>144</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>145</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>146</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -3532,7 +3506,7 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -3594,7 +3568,7 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
@@ -3668,7 +3642,7 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -3748,7 +3722,7 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -3828,7 +3802,7 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
@@ -3890,7 +3864,7 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
@@ -3899,9 +3873,6 @@
       <c r="C8" t="s">
         <v>121</v>
       </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
       <c r="E8" t="s">
         <v>121</v>
       </c>
@@ -3920,33 +3891,21 @@
       <c r="J8" t="s">
         <v>121</v>
       </c>
-      <c r="K8" t="s">
-        <v>121</v>
-      </c>
       <c r="L8" t="s">
         <v>121</v>
       </c>
-      <c r="M8" t="s">
-        <v>121</v>
-      </c>
       <c r="N8" t="s">
         <v>121</v>
       </c>
       <c r="O8" t="s">
         <v>121</v>
       </c>
-      <c r="P8" t="s">
-        <v>121</v>
-      </c>
       <c r="Q8" t="s">
         <v>121</v>
       </c>
       <c r="R8" t="s">
         <v>121</v>
       </c>
-      <c r="S8" t="s">
-        <v>121</v>
-      </c>
       <c r="T8" t="s">
         <v>121</v>
       </c>
@@ -3973,7 +3932,7 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
@@ -4053,7 +4012,7 @@
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
@@ -4106,7 +4065,7 @@
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="s">
@@ -4129,7 +4088,7 @@
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
@@ -4188,7 +4147,7 @@
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
@@ -4241,7 +4200,7 @@
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
@@ -4297,7 +4256,7 @@
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
@@ -4374,7 +4333,7 @@
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
@@ -4421,7 +4380,7 @@
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
@@ -4489,7 +4448,7 @@
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
@@ -4551,7 +4510,7 @@
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
@@ -4604,7 +4563,7 @@
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
@@ -4672,7 +4631,7 @@
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
@@ -4755,7 +4714,7 @@
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
@@ -4826,7 +4785,7 @@
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
@@ -4882,7 +4841,7 @@
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" t="s">
@@ -4959,7 +4918,7 @@
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25" t="s">
@@ -5030,7 +4989,7 @@
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26" t="s">
@@ -5104,7 +5063,7 @@
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27" t="s">
@@ -5172,7 +5131,7 @@
       </c>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28" t="s">
@@ -5225,7 +5184,7 @@
       </c>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
@@ -5296,7 +5255,7 @@
       </c>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
@@ -5379,7 +5338,7 @@
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
@@ -5450,7 +5409,7 @@
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32" t="s">
@@ -5500,7 +5459,7 @@
       </c>
     </row>
     <row r="33" spans="1:27">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
@@ -5583,7 +5542,7 @@
       </c>
     </row>
     <row r="34" spans="1:27">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34" t="s">
@@ -5642,7 +5601,7 @@
       </c>
     </row>
     <row r="35" spans="1:27">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35" t="s">
@@ -5713,7 +5672,7 @@
       </c>
     </row>
     <row r="36" spans="1:27">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="B36" t="s">
@@ -5781,7 +5740,7 @@
       </c>
     </row>
     <row r="37" spans="1:27">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37" t="s">
@@ -5834,7 +5793,7 @@
       </c>
     </row>
     <row r="38" spans="1:27">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38" t="s">
@@ -5905,7 +5864,7 @@
       </c>
     </row>
     <row r="39" spans="1:27">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39" t="s">
@@ -5967,7 +5926,7 @@
       </c>
     </row>
     <row r="40" spans="1:27">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40" t="s">
@@ -6038,7 +5997,7 @@
       </c>
     </row>
     <row r="41" spans="1:27">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41" t="s">
@@ -6106,7 +6065,7 @@
       </c>
     </row>
     <row r="42" spans="1:27">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="C42" t="s">
@@ -6135,7 +6094,7 @@
       </c>
     </row>
     <row r="43" spans="1:27">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43" t="s">
@@ -6209,7 +6168,7 @@
       </c>
     </row>
     <row r="44" spans="1:27">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="C44" t="s">
@@ -6241,7 +6200,7 @@
       </c>
     </row>
     <row r="45" spans="1:27">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="C45" t="s">
@@ -6276,7 +6235,7 @@
       </c>
     </row>
     <row r="46" spans="1:27">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46" t="s">
@@ -6350,7 +6309,7 @@
       </c>
     </row>
     <row r="47" spans="1:27">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="B47" t="s">
@@ -6391,7 +6350,7 @@
       </c>
     </row>
     <row r="48" spans="1:27">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48" t="s">
@@ -6432,7 +6391,7 @@
       </c>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49" t="s">
@@ -6503,7 +6462,7 @@
       </c>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50" t="s">
@@ -6550,7 +6509,7 @@
       </c>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="B51" t="s">
@@ -6627,7 +6586,7 @@
       </c>
     </row>
     <row r="52" spans="1:27">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="B52" t="s">
@@ -6698,7 +6657,7 @@
       </c>
     </row>
     <row r="53" spans="1:27">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53" t="s">
@@ -6769,7 +6728,7 @@
       </c>
     </row>
     <row r="54" spans="1:27">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54" t="s">
@@ -6825,7 +6784,7 @@
       </c>
     </row>
     <row r="55" spans="1:27">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55" t="s">
@@ -6905,7 +6864,7 @@
       </c>
     </row>
     <row r="56" spans="1:27">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>61</v>
       </c>
       <c r="B56" t="s">
@@ -6955,7 +6914,7 @@
       </c>
     </row>
     <row r="57" spans="1:27">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>62</v>
       </c>
       <c r="B57" t="s">
@@ -7020,7 +6979,7 @@
       </c>
     </row>
     <row r="58" spans="1:27">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58" t="s">
@@ -7094,7 +7053,7 @@
       </c>
     </row>
     <row r="59" spans="1:27">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="B59" t="s">
@@ -7156,7 +7115,7 @@
       </c>
     </row>
     <row r="60" spans="1:27">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60" t="s">
@@ -7215,7 +7174,7 @@
       </c>
     </row>
     <row r="61" spans="1:27">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>66</v>
       </c>
       <c r="B61" t="s">
@@ -7289,7 +7248,7 @@
       </c>
     </row>
     <row r="62" spans="1:27">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62" t="s">
@@ -7348,7 +7307,7 @@
       </c>
     </row>
     <row r="63" spans="1:27">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="B63" t="s">
@@ -7386,7 +7345,7 @@
       </c>
     </row>
     <row r="64" spans="1:27">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>69</v>
       </c>
       <c r="B64" t="s">
@@ -7454,7 +7413,7 @@
       </c>
     </row>
     <row r="65" spans="1:27">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65" t="s">
@@ -7528,7 +7487,7 @@
       </c>
     </row>
     <row r="66" spans="1:27">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>71</v>
       </c>
       <c r="B66" t="s">
@@ -7602,7 +7561,7 @@
       </c>
     </row>
     <row r="67" spans="1:27">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>72</v>
       </c>
       <c r="B67" t="s">
@@ -7664,7 +7623,7 @@
       </c>
     </row>
     <row r="68" spans="1:27">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>73</v>
       </c>
       <c r="C68" t="s">
@@ -7702,7 +7661,7 @@
       </c>
     </row>
     <row r="69" spans="1:27">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>74</v>
       </c>
       <c r="B69" t="s">
@@ -7770,7 +7729,7 @@
       </c>
     </row>
     <row r="70" spans="1:27">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>75</v>
       </c>
       <c r="B70" t="s">
@@ -7835,7 +7794,7 @@
       </c>
     </row>
     <row r="71" spans="1:27">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>76</v>
       </c>
       <c r="B71" t="s">
@@ -7879,7 +7838,7 @@
       </c>
     </row>
     <row r="72" spans="1:27">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>77</v>
       </c>
       <c r="C72" t="s">
@@ -7923,7 +7882,7 @@
       </c>
     </row>
     <row r="73" spans="1:27">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>78</v>
       </c>
       <c r="B73" t="s">
@@ -7988,7 +7947,7 @@
       </c>
     </row>
     <row r="74" spans="1:27">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>79</v>
       </c>
       <c r="B74" t="s">
@@ -8056,7 +8015,7 @@
       </c>
     </row>
     <row r="75" spans="1:27">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>80</v>
       </c>
       <c r="B75" t="s">
@@ -8127,7 +8086,7 @@
       </c>
     </row>
     <row r="76" spans="1:27">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>81</v>
       </c>
       <c r="B76" t="s">
@@ -8201,7 +8160,7 @@
       </c>
     </row>
     <row r="77" spans="1:27">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>82</v>
       </c>
       <c r="B77" t="s">
@@ -8269,7 +8228,7 @@
       </c>
     </row>
     <row r="78" spans="1:27">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>83</v>
       </c>
       <c r="M78" t="s">
@@ -8289,7 +8248,7 @@
       </c>
     </row>
     <row r="79" spans="1:27">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>84</v>
       </c>
       <c r="B79" t="s">
@@ -8372,7 +8331,7 @@
       </c>
     </row>
     <row r="80" spans="1:27">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>85</v>
       </c>
       <c r="B80" t="s">
@@ -8443,7 +8402,7 @@
       </c>
     </row>
     <row r="81" spans="1:27">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>86</v>
       </c>
       <c r="B81" t="s">
@@ -8514,7 +8473,7 @@
       </c>
     </row>
     <row r="82" spans="1:27">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>87</v>
       </c>
       <c r="B82" t="s">
@@ -8594,7 +8553,7 @@
       </c>
     </row>
     <row r="83" spans="1:27">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>88</v>
       </c>
       <c r="B83" t="s">
@@ -8674,7 +8633,7 @@
       </c>
     </row>
     <row r="84" spans="1:27">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>89</v>
       </c>
       <c r="B84" t="s">
@@ -8754,7 +8713,7 @@
       </c>
     </row>
     <row r="85" spans="1:27">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>90</v>
       </c>
       <c r="B85" t="s">
@@ -8828,7 +8787,7 @@
       </c>
     </row>
     <row r="86" spans="1:27">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>91</v>
       </c>
       <c r="B86" t="s">
@@ -8902,7 +8861,7 @@
       </c>
     </row>
     <row r="87" spans="1:27">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>92</v>
       </c>
       <c r="B87" t="s">
@@ -8979,7 +8938,7 @@
       </c>
     </row>
     <row r="88" spans="1:27">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>93</v>
       </c>
       <c r="B88" t="s">
@@ -9059,7 +9018,7 @@
       </c>
     </row>
     <row r="89" spans="1:27">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>94</v>
       </c>
       <c r="B89" t="s">
@@ -9130,7 +9089,7 @@
       </c>
     </row>
     <row r="90" spans="1:27">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>95</v>
       </c>
       <c r="B90" t="s">
@@ -9198,7 +9157,7 @@
       </c>
     </row>
     <row r="91" spans="1:27">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>96</v>
       </c>
       <c r="B91" t="s">
@@ -9272,7 +9231,7 @@
       </c>
     </row>
     <row r="92" spans="1:27">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>97</v>
       </c>
       <c r="B92" t="s">
@@ -9337,7 +9296,7 @@
       </c>
     </row>
     <row r="93" spans="1:27">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>98</v>
       </c>
       <c r="B93" t="s">
@@ -9417,7 +9376,7 @@
       </c>
     </row>
     <row r="94" spans="1:27">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>99</v>
       </c>
       <c r="B94" t="s">
@@ -9488,7 +9447,7 @@
       </c>
     </row>
     <row r="95" spans="1:27">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>100</v>
       </c>
       <c r="B95" t="s">
@@ -9568,7 +9527,7 @@
       </c>
     </row>
     <row r="96" spans="1:27">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>101</v>
       </c>
       <c r="B96" t="s">
@@ -9639,7 +9598,7 @@
       </c>
     </row>
     <row r="97" spans="1:27">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>102</v>
       </c>
       <c r="B97" t="s">
@@ -9701,7 +9660,7 @@
       </c>
     </row>
     <row r="98" spans="1:27">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>103</v>
       </c>
       <c r="B98" t="s">
@@ -9763,7 +9722,7 @@
       </c>
     </row>
     <row r="99" spans="1:27">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>104</v>
       </c>
       <c r="B99" t="s">
@@ -9843,7 +9802,7 @@
       </c>
     </row>
     <row r="100" spans="1:27">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>105</v>
       </c>
       <c r="B100" t="s">
@@ -9914,7 +9873,7 @@
       </c>
     </row>
     <row r="101" spans="1:27">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>106</v>
       </c>
       <c r="B101" t="s">
@@ -9991,7 +9950,7 @@
       </c>
     </row>
     <row r="102" spans="1:27">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>107</v>
       </c>
       <c r="B102" t="s">
@@ -10068,7 +10027,7 @@
       </c>
     </row>
     <row r="103" spans="1:27">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>108</v>
       </c>
       <c r="B103" t="s">
@@ -10148,7 +10107,7 @@
       </c>
     </row>
     <row r="104" spans="1:27">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>109</v>
       </c>
       <c r="B104" t="s">
@@ -10222,7 +10181,7 @@
       </c>
     </row>
     <row r="105" spans="1:27">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>110</v>
       </c>
       <c r="B105" t="s">
@@ -10290,7 +10249,7 @@
       </c>
     </row>
     <row r="106" spans="1:27">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>111</v>
       </c>
       <c r="B106" t="s">
@@ -10361,7 +10320,7 @@
       </c>
     </row>
     <row r="107" spans="1:27">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>112</v>
       </c>
       <c r="B107" t="s">
@@ -10417,7 +10376,7 @@
       </c>
     </row>
     <row r="108" spans="1:27">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>113</v>
       </c>
       <c r="B108" t="s">
@@ -10494,7 +10453,7 @@
       </c>
     </row>
     <row r="109" spans="1:27">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>114</v>
       </c>
       <c r="B109" t="s">
@@ -10577,7 +10536,7 @@
       </c>
     </row>
     <row r="110" spans="1:27">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>115</v>
       </c>
       <c r="B110" t="s">
@@ -10657,7 +10616,7 @@
       </c>
     </row>
     <row r="111" spans="1:27">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>116</v>
       </c>
       <c r="B111" t="s">
@@ -10725,7 +10684,7 @@
       </c>
     </row>
     <row r="112" spans="1:27">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>117</v>
       </c>
       <c r="B112" t="s">
@@ -10805,7 +10764,7 @@
       </c>
     </row>
     <row r="113" spans="1:27">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>118</v>
       </c>
       <c r="B113" t="s">
@@ -10885,7 +10844,7 @@
       </c>
     </row>
     <row r="114" spans="1:27">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>119</v>
       </c>
       <c r="C114" t="s">
@@ -10941,7 +10900,7 @@
       </c>
     </row>
     <row r="115" spans="1:27">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>120</v>
       </c>
       <c r="B115" t="s">
@@ -11025,90 +10984,90 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>151</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>152</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>154</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>155</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>156</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>157</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>158</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>159</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>160</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>161</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>162</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>163</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>164</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>165</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>166</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>167</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>168</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>169</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>170</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>171</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>172</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -11161,7 +11120,7 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
@@ -11223,7 +11182,7 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
@@ -11297,7 +11256,7 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
@@ -11377,7 +11336,7 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
@@ -11457,7 +11416,7 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
@@ -11519,12 +11478,9 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>121</v>
-      </c>
       <c r="C8" t="s">
         <v>121</v>
       </c>
@@ -11561,9 +11517,6 @@
       <c r="N8" t="s">
         <v>121</v>
       </c>
-      <c r="O8" t="s">
-        <v>121</v>
-      </c>
       <c r="P8" t="s">
         <v>121</v>
       </c>
@@ -11579,21 +11532,12 @@
       <c r="T8" t="s">
         <v>121</v>
       </c>
-      <c r="U8" t="s">
-        <v>121</v>
-      </c>
       <c r="V8" t="s">
         <v>121</v>
       </c>
       <c r="W8" t="s">
         <v>121</v>
       </c>
-      <c r="X8" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>121</v>
-      </c>
       <c r="Z8" t="s">
         <v>121</v>
       </c>
@@ -11602,7 +11546,7 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
@@ -11682,7 +11626,7 @@
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
@@ -11735,7 +11679,7 @@
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="H11" t="s">
@@ -11758,7 +11702,7 @@
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
@@ -11817,7 +11761,7 @@
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
@@ -11870,7 +11814,7 @@
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
@@ -11926,7 +11870,7 @@
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
@@ -12003,7 +11947,7 @@
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
@@ -12050,7 +11994,7 @@
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
@@ -12118,7 +12062,7 @@
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
@@ -12180,7 +12124,7 @@
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
@@ -12233,7 +12177,7 @@
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="E20" t="s">
@@ -12301,7 +12245,7 @@
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
@@ -12384,7 +12328,7 @@
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="C22" t="s">
@@ -12455,7 +12399,7 @@
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -12511,7 +12455,7 @@
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" t="s">
@@ -12588,7 +12532,7 @@
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="C25" t="s">
@@ -12659,7 +12603,7 @@
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="C26" t="s">
@@ -12733,7 +12677,7 @@
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="C27" t="s">
@@ -12801,7 +12745,7 @@
       </c>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="C28" t="s">
@@ -12854,7 +12798,7 @@
       </c>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="C29" t="s">
@@ -12925,7 +12869,7 @@
       </c>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
@@ -13008,7 +12952,7 @@
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="E31" t="s">
@@ -13079,7 +13023,7 @@
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="C32" t="s">
@@ -13129,7 +13073,7 @@
       </c>
     </row>
     <row r="33" spans="1:27">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
@@ -13212,7 +13156,7 @@
       </c>
     </row>
     <row r="34" spans="1:27">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="C34" t="s">
@@ -13271,7 +13215,7 @@
       </c>
     </row>
     <row r="35" spans="1:27">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="C35" t="s">
@@ -13342,7 +13286,7 @@
       </c>
     </row>
     <row r="36" spans="1:27">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="E36" t="s">
@@ -13410,7 +13354,7 @@
       </c>
     </row>
     <row r="37" spans="1:27">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="E37" t="s">
@@ -13463,7 +13407,7 @@
       </c>
     </row>
     <row r="38" spans="1:27">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="C38" t="s">
@@ -13534,7 +13478,7 @@
       </c>
     </row>
     <row r="39" spans="1:27">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="C39" t="s">
@@ -13596,7 +13540,7 @@
       </c>
     </row>
     <row r="40" spans="1:27">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="C40" t="s">
@@ -13667,7 +13611,7 @@
       </c>
     </row>
     <row r="41" spans="1:27">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="C41" t="s">
@@ -13735,7 +13679,7 @@
       </c>
     </row>
     <row r="42" spans="1:27">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="M42" t="s">
@@ -13764,7 +13708,7 @@
       </c>
     </row>
     <row r="43" spans="1:27">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="E43" t="s">
@@ -13838,7 +13782,7 @@
       </c>
     </row>
     <row r="44" spans="1:27">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="C44" t="s">
@@ -13870,7 +13814,7 @@
       </c>
     </row>
     <row r="45" spans="1:27">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="C45" t="s">
@@ -13905,7 +13849,7 @@
       </c>
     </row>
     <row r="46" spans="1:27">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="C46" t="s">
@@ -13979,7 +13923,7 @@
       </c>
     </row>
     <row r="47" spans="1:27">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="E47" t="s">
@@ -14020,7 +13964,7 @@
       </c>
     </row>
     <row r="48" spans="1:27">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="F48" t="s">
@@ -14061,7 +14005,7 @@
       </c>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="C49" t="s">
@@ -14132,7 +14076,7 @@
       </c>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="C50" t="s">
@@ -14179,7 +14123,7 @@
       </c>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="C51" t="s">
@@ -14256,7 +14200,7 @@
       </c>
     </row>
     <row r="52" spans="1:27">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="C52" t="s">
@@ -14327,7 +14271,7 @@
       </c>
     </row>
     <row r="53" spans="1:27">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="C53" t="s">
@@ -14398,7 +14342,7 @@
       </c>
     </row>
     <row r="54" spans="1:27">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="C54" t="s">
@@ -14454,7 +14398,7 @@
       </c>
     </row>
     <row r="55" spans="1:27">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="C55" t="s">
@@ -14534,7 +14478,7 @@
       </c>
     </row>
     <row r="56" spans="1:27">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>61</v>
       </c>
       <c r="C56" t="s">
@@ -14584,7 +14528,7 @@
       </c>
     </row>
     <row r="57" spans="1:27">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>62</v>
       </c>
       <c r="C57" t="s">
@@ -14649,7 +14593,7 @@
       </c>
     </row>
     <row r="58" spans="1:27">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="C58" t="s">
@@ -14723,7 +14667,7 @@
       </c>
     </row>
     <row r="59" spans="1:27">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="C59" t="s">
@@ -14785,7 +14729,7 @@
       </c>
     </row>
     <row r="60" spans="1:27">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="C60" t="s">
@@ -14844,7 +14788,7 @@
       </c>
     </row>
     <row r="61" spans="1:27">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>66</v>
       </c>
       <c r="C61" t="s">
@@ -14918,7 +14862,7 @@
       </c>
     </row>
     <row r="62" spans="1:27">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="C62" t="s">
@@ -14977,7 +14921,7 @@
       </c>
     </row>
     <row r="63" spans="1:27">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="G63" t="s">
@@ -15015,7 +14959,7 @@
       </c>
     </row>
     <row r="64" spans="1:27">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>69</v>
       </c>
       <c r="C64" t="s">
@@ -15083,7 +15027,7 @@
       </c>
     </row>
     <row r="65" spans="1:27">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="C65" t="s">
@@ -15157,7 +15101,7 @@
       </c>
     </row>
     <row r="66" spans="1:27">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>71</v>
       </c>
       <c r="C66" t="s">
@@ -15231,7 +15175,7 @@
       </c>
     </row>
     <row r="67" spans="1:27">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>72</v>
       </c>
       <c r="C67" t="s">
@@ -15293,7 +15237,7 @@
       </c>
     </row>
     <row r="68" spans="1:27">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>73</v>
       </c>
       <c r="C68" t="s">
@@ -15331,7 +15275,7 @@
       </c>
     </row>
     <row r="69" spans="1:27">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>74</v>
       </c>
       <c r="C69" t="s">
@@ -15399,7 +15343,7 @@
       </c>
     </row>
     <row r="70" spans="1:27">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>75</v>
       </c>
       <c r="C70" t="s">
@@ -15464,7 +15408,7 @@
       </c>
     </row>
     <row r="71" spans="1:27">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>76</v>
       </c>
       <c r="C71" t="s">
@@ -15508,7 +15452,7 @@
       </c>
     </row>
     <row r="72" spans="1:27">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>77</v>
       </c>
       <c r="C72" t="s">
@@ -15552,7 +15496,7 @@
       </c>
     </row>
     <row r="73" spans="1:27">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>78</v>
       </c>
       <c r="C73" t="s">
@@ -15617,7 +15561,7 @@
       </c>
     </row>
     <row r="74" spans="1:27">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>79</v>
       </c>
       <c r="C74" t="s">
@@ -15685,7 +15629,7 @@
       </c>
     </row>
     <row r="75" spans="1:27">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>80</v>
       </c>
       <c r="E75" t="s">
@@ -15756,7 +15700,7 @@
       </c>
     </row>
     <row r="76" spans="1:27">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>81</v>
       </c>
       <c r="C76" t="s">
@@ -15830,7 +15774,7 @@
       </c>
     </row>
     <row r="77" spans="1:27">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>82</v>
       </c>
       <c r="C77" t="s">
@@ -15898,7 +15842,7 @@
       </c>
     </row>
     <row r="78" spans="1:27">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>83</v>
       </c>
       <c r="H78" t="s">
@@ -15918,7 +15862,7 @@
       </c>
     </row>
     <row r="79" spans="1:27">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>84</v>
       </c>
       <c r="B79" t="s">
@@ -16001,7 +15945,7 @@
       </c>
     </row>
     <row r="80" spans="1:27">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>85</v>
       </c>
       <c r="E80" t="s">
@@ -16072,7 +16016,7 @@
       </c>
     </row>
     <row r="81" spans="1:27">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>86</v>
       </c>
       <c r="C81" t="s">
@@ -16143,7 +16087,7 @@
       </c>
     </row>
     <row r="82" spans="1:27">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>87</v>
       </c>
       <c r="C82" t="s">
@@ -16223,7 +16167,7 @@
       </c>
     </row>
     <row r="83" spans="1:27">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>88</v>
       </c>
       <c r="B83" t="s">
@@ -16303,7 +16247,7 @@
       </c>
     </row>
     <row r="84" spans="1:27">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>89</v>
       </c>
       <c r="C84" t="s">
@@ -16383,7 +16327,7 @@
       </c>
     </row>
     <row r="85" spans="1:27">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>90</v>
       </c>
       <c r="C85" t="s">
@@ -16457,7 +16401,7 @@
       </c>
     </row>
     <row r="86" spans="1:27">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>91</v>
       </c>
       <c r="E86" t="s">
@@ -16531,7 +16475,7 @@
       </c>
     </row>
     <row r="87" spans="1:27">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>92</v>
       </c>
       <c r="C87" t="s">
@@ -16608,7 +16552,7 @@
       </c>
     </row>
     <row r="88" spans="1:27">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>93</v>
       </c>
       <c r="C88" t="s">
@@ -16688,7 +16632,7 @@
       </c>
     </row>
     <row r="89" spans="1:27">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>94</v>
       </c>
       <c r="C89" t="s">
@@ -16759,7 +16703,7 @@
       </c>
     </row>
     <row r="90" spans="1:27">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>95</v>
       </c>
       <c r="C90" t="s">
@@ -16827,7 +16771,7 @@
       </c>
     </row>
     <row r="91" spans="1:27">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>96</v>
       </c>
       <c r="C91" t="s">
@@ -16901,7 +16845,7 @@
       </c>
     </row>
     <row r="92" spans="1:27">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>97</v>
       </c>
       <c r="E92" t="s">
@@ -16966,7 +16910,7 @@
       </c>
     </row>
     <row r="93" spans="1:27">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>98</v>
       </c>
       <c r="C93" t="s">
@@ -17046,7 +16990,7 @@
       </c>
     </row>
     <row r="94" spans="1:27">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>99</v>
       </c>
       <c r="C94" t="s">
@@ -17117,7 +17061,7 @@
       </c>
     </row>
     <row r="95" spans="1:27">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>100</v>
       </c>
       <c r="C95" t="s">
@@ -17197,7 +17141,7 @@
       </c>
     </row>
     <row r="96" spans="1:27">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>101</v>
       </c>
       <c r="C96" t="s">
@@ -17268,7 +17212,7 @@
       </c>
     </row>
     <row r="97" spans="1:27">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>102</v>
       </c>
       <c r="C97" t="s">
@@ -17330,7 +17274,7 @@
       </c>
     </row>
     <row r="98" spans="1:27">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>103</v>
       </c>
       <c r="C98" t="s">
@@ -17392,7 +17336,7 @@
       </c>
     </row>
     <row r="99" spans="1:27">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>104</v>
       </c>
       <c r="C99" t="s">
@@ -17472,7 +17416,7 @@
       </c>
     </row>
     <row r="100" spans="1:27">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>105</v>
       </c>
       <c r="C100" t="s">
@@ -17543,7 +17487,7 @@
       </c>
     </row>
     <row r="101" spans="1:27">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>106</v>
       </c>
       <c r="C101" t="s">
@@ -17620,7 +17564,7 @@
       </c>
     </row>
     <row r="102" spans="1:27">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>107</v>
       </c>
       <c r="C102" t="s">
@@ -17697,7 +17641,7 @@
       </c>
     </row>
     <row r="103" spans="1:27">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>108</v>
       </c>
       <c r="C103" t="s">
@@ -17777,7 +17721,7 @@
       </c>
     </row>
     <row r="104" spans="1:27">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>109</v>
       </c>
       <c r="C104" t="s">
@@ -17851,7 +17795,7 @@
       </c>
     </row>
     <row r="105" spans="1:27">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>110</v>
       </c>
       <c r="C105" t="s">
@@ -17919,7 +17863,7 @@
       </c>
     </row>
     <row r="106" spans="1:27">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>111</v>
       </c>
       <c r="C106" t="s">
@@ -17990,7 +17934,7 @@
       </c>
     </row>
     <row r="107" spans="1:27">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>112</v>
       </c>
       <c r="E107" t="s">
@@ -18046,7 +17990,7 @@
       </c>
     </row>
     <row r="108" spans="1:27">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>113</v>
       </c>
       <c r="C108" t="s">
@@ -18123,7 +18067,7 @@
       </c>
     </row>
     <row r="109" spans="1:27">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>114</v>
       </c>
       <c r="B109" t="s">
@@ -18206,7 +18150,7 @@
       </c>
     </row>
     <row r="110" spans="1:27">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>115</v>
       </c>
       <c r="C110" t="s">
@@ -18286,7 +18230,7 @@
       </c>
     </row>
     <row r="111" spans="1:27">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>116</v>
       </c>
       <c r="C111" t="s">
@@ -18354,7 +18298,7 @@
       </c>
     </row>
     <row r="112" spans="1:27">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>117</v>
       </c>
       <c r="C112" t="s">
@@ -18434,7 +18378,7 @@
       </c>
     </row>
     <row r="113" spans="1:27">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>118</v>
       </c>
       <c r="C113" t="s">
@@ -18514,7 +18458,7 @@
       </c>
     </row>
     <row r="114" spans="1:27">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>119</v>
       </c>
       <c r="C114" t="s">
@@ -18570,7 +18514,7 @@
       </c>
     </row>
     <row r="115" spans="1:27">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>120</v>
       </c>
       <c r="C115" t="s">
@@ -18654,16 +18598,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
+      <c r="A2" t="s">
+        <v>26</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -18673,8 +18617,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
+      <c r="A3" t="s">
+        <v>35</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -18684,8 +18628,8 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>35</v>
+      <c r="A4" t="s">
+        <v>38</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -18695,8 +18639,8 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>38</v>
+      <c r="A5" t="s">
+        <v>84</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -18706,8 +18650,8 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>84</v>
+      <c r="A6" t="s">
+        <v>114</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -18717,19 +18661,19 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>114</v>
+      <c r="A7" t="s">
+        <v>10</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -18739,8 +18683,8 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
+      <c r="A9" t="s">
+        <v>14</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -18750,8 +18694,8 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
+      <c r="A10" t="s">
+        <v>60</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -18761,8 +18705,8 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>60</v>
+      <c r="A11" t="s">
+        <v>87</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -18772,8 +18716,8 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>87</v>
+      <c r="A12" t="s">
+        <v>88</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -18783,8 +18727,8 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>88</v>
+      <c r="A13" t="s">
+        <v>89</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -18794,8 +18738,8 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>89</v>
+      <c r="A14" t="s">
+        <v>93</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -18805,8 +18749,8 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>93</v>
+      <c r="A15" t="s">
+        <v>98</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -18816,8 +18760,8 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>98</v>
+      <c r="A16" t="s">
+        <v>100</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -18827,8 +18771,8 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>100</v>
+      <c r="A17" t="s">
+        <v>104</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -18838,8 +18782,8 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>104</v>
+      <c r="A18" t="s">
+        <v>108</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -18849,8 +18793,8 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>108</v>
+      <c r="A19" t="s">
+        <v>115</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -18860,8 +18804,8 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>115</v>
+      <c r="A20" t="s">
+        <v>117</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -18871,8 +18815,8 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>117</v>
+      <c r="A21" t="s">
+        <v>118</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -18882,19 +18826,19 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>118</v>
+      <c r="A22" t="s">
+        <v>20</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
+      <c r="A23" t="s">
+        <v>29</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -18904,8 +18848,8 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
+      <c r="A24" t="s">
+        <v>56</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -18915,8 +18859,8 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="1" t="s">
-        <v>56</v>
+      <c r="A25" t="s">
+        <v>92</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -18926,8 +18870,8 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>92</v>
+      <c r="A26" t="s">
+        <v>106</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -18937,8 +18881,8 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>106</v>
+      <c r="A27" t="s">
+        <v>107</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -18948,8 +18892,8 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>107</v>
+      <c r="A28" t="s">
+        <v>113</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -18959,19 +18903,19 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>113</v>
+      <c r="A29" t="s">
+        <v>9</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="1" t="s">
-        <v>9</v>
+      <c r="A30" t="s">
+        <v>31</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -18981,8 +18925,8 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>31</v>
+      <c r="A31" t="s">
+        <v>51</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -18992,8 +18936,8 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
+      <c r="A32" t="s">
+        <v>63</v>
       </c>
       <c r="B32">
         <v>6</v>
@@ -19003,8 +18947,8 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>63</v>
+      <c r="A33" t="s">
+        <v>66</v>
       </c>
       <c r="B33">
         <v>6</v>
@@ -19014,8 +18958,8 @@
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="1" t="s">
-        <v>66</v>
+      <c r="A34" t="s">
+        <v>70</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -19025,8 +18969,8 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
-        <v>70</v>
+      <c r="A35" t="s">
+        <v>71</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -19036,8 +18980,8 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
-        <v>71</v>
+      <c r="A36" t="s">
+        <v>81</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -19047,8 +18991,8 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="1" t="s">
-        <v>81</v>
+      <c r="A37" t="s">
+        <v>90</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -19058,8 +19002,8 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="1" t="s">
-        <v>90</v>
+      <c r="A38" t="s">
+        <v>96</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -19069,8 +19013,8 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>96</v>
+      <c r="A39" t="s">
+        <v>109</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -19080,8 +19024,8 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>109</v>
+      <c r="A40" t="s">
+        <v>120</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -19091,19 +19035,19 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
-        <v>120</v>
+      <c r="A41" t="s">
+        <v>27</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
+      <c r="A42" t="s">
+        <v>30</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -19113,8 +19057,8 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>30</v>
+      <c r="A43" t="s">
+        <v>34</v>
       </c>
       <c r="B43">
         <v>6</v>
@@ -19124,8 +19068,8 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
-        <v>34</v>
+      <c r="A44" t="s">
+        <v>40</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -19135,8 +19079,8 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
-        <v>40</v>
+      <c r="A45" t="s">
+        <v>43</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -19146,8 +19090,8 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
-        <v>43</v>
+      <c r="A46" t="s">
+        <v>45</v>
       </c>
       <c r="B46">
         <v>6</v>
@@ -19157,8 +19101,8 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
-        <v>45</v>
+      <c r="A47" t="s">
+        <v>54</v>
       </c>
       <c r="B47">
         <v>6</v>
@@ -19168,8 +19112,8 @@
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
+      <c r="A48" t="s">
+        <v>57</v>
       </c>
       <c r="B48">
         <v>6</v>
@@ -19179,8 +19123,8 @@
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>57</v>
+      <c r="A49" t="s">
+        <v>58</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -19190,8 +19134,8 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>58</v>
+      <c r="A50" t="s">
+        <v>86</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -19201,8 +19145,8 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>86</v>
+      <c r="A51" t="s">
+        <v>94</v>
       </c>
       <c r="B51">
         <v>6</v>
@@ -19212,8 +19156,8 @@
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>94</v>
+      <c r="A52" t="s">
+        <v>99</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -19223,8 +19167,8 @@
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>99</v>
+      <c r="A53" t="s">
+        <v>101</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -19234,8 +19178,8 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
-        <v>101</v>
+      <c r="A54" t="s">
+        <v>105</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -19245,8 +19189,8 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
-        <v>105</v>
+      <c r="A55" t="s">
+        <v>111</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -19256,18 +19200,18 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="1" t="s">
-        <v>111</v>
+      <c r="A56" t="s">
+        <v>13</v>
       </c>
       <c r="B56">
         <v>6</v>
       </c>
       <c r="C56">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>22</v>
       </c>
       <c r="B57">
@@ -19278,7 +19222,7 @@
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>32</v>
       </c>
       <c r="B58">
@@ -19289,7 +19233,7 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>46</v>
       </c>
       <c r="B59">
@@ -19300,7 +19244,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>69</v>
       </c>
       <c r="B60">
@@ -19311,7 +19255,7 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>74</v>
       </c>
       <c r="B61">
@@ -19322,7 +19266,7 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>79</v>
       </c>
       <c r="B62">
@@ -19333,7 +19277,7 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>82</v>
       </c>
       <c r="B63">
@@ -19344,7 +19288,7 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>95</v>
       </c>
       <c r="B64">
@@ -19355,7 +19299,7 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>110</v>
       </c>
       <c r="B65">
@@ -19366,7 +19310,7 @@
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>116</v>
       </c>
       <c r="B66">
@@ -19377,7 +19321,7 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>62</v>
       </c>
       <c r="B67">
@@ -19388,7 +19332,7 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>75</v>
       </c>
       <c r="B68">
@@ -19399,7 +19343,7 @@
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>78</v>
       </c>
       <c r="B69">
@@ -19410,7 +19354,7 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>8</v>
       </c>
       <c r="B70">
@@ -19421,7 +19365,7 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>23</v>
       </c>
       <c r="B71">
@@ -19432,7 +19376,7 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>44</v>
       </c>
       <c r="B72">
@@ -19443,7 +19387,7 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>64</v>
       </c>
       <c r="B73">
@@ -19454,7 +19398,7 @@
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>72</v>
       </c>
       <c r="B74">
@@ -19465,7 +19409,7 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>102</v>
       </c>
       <c r="B75">
@@ -19476,7 +19420,7 @@
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>103</v>
       </c>
       <c r="B76">
@@ -19487,7 +19431,7 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>65</v>
       </c>
       <c r="B77">
@@ -19498,7 +19442,7 @@
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>67</v>
       </c>
       <c r="B78">
@@ -19509,7 +19453,7 @@
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>7</v>
       </c>
       <c r="B79">
@@ -19520,7 +19464,7 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>33</v>
       </c>
       <c r="B80">
@@ -19531,7 +19475,7 @@
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>76</v>
       </c>
       <c r="B81">
@@ -19542,7 +19486,7 @@
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>48</v>
       </c>
       <c r="B82">
@@ -19553,7 +19497,7 @@
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>91</v>
       </c>
       <c r="B83">
@@ -19564,7 +19508,7 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>36</v>
       </c>
       <c r="B84">
@@ -19575,7 +19519,7 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>80</v>
       </c>
       <c r="B85">
@@ -19586,7 +19530,7 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>85</v>
       </c>
       <c r="B86">
@@ -19597,7 +19541,7 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>25</v>
       </c>
       <c r="B87">
@@ -19608,7 +19552,7 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>41</v>
       </c>
       <c r="B88">
@@ -19619,7 +19563,7 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>97</v>
       </c>
       <c r="B89">
@@ -19630,7 +19574,7 @@
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>12</v>
       </c>
       <c r="B90">
@@ -19641,7 +19585,7 @@
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>17</v>
       </c>
       <c r="B91">
@@ -19652,7 +19596,7 @@
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>39</v>
       </c>
       <c r="B92">
@@ -19663,7 +19607,7 @@
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>19</v>
       </c>
       <c r="B93">
@@ -19674,7 +19618,7 @@
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>28</v>
       </c>
       <c r="B94">
@@ -19685,7 +19629,7 @@
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>59</v>
       </c>
       <c r="B95">
@@ -19696,7 +19640,7 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>112</v>
       </c>
       <c r="B96">
@@ -19707,7 +19651,7 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>119</v>
       </c>
       <c r="B97">
@@ -19718,7 +19662,7 @@
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>18</v>
       </c>
       <c r="B98">
@@ -19729,7 +19673,7 @@
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>24</v>
       </c>
       <c r="B99">
@@ -19740,7 +19684,7 @@
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>42</v>
       </c>
       <c r="B100">
@@ -19751,7 +19695,7 @@
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>37</v>
       </c>
       <c r="B101">
@@ -19762,7 +19706,7 @@
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>61</v>
       </c>
       <c r="B102">
@@ -19773,7 +19717,7 @@
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>15</v>
       </c>
       <c r="B103">
@@ -19784,7 +19728,7 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>21</v>
       </c>
       <c r="B104">
@@ -19795,7 +19739,7 @@
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>55</v>
       </c>
       <c r="B105">
@@ -19806,7 +19750,7 @@
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>77</v>
       </c>
       <c r="B106">
@@ -19817,7 +19761,7 @@
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>53</v>
       </c>
       <c r="B107">
@@ -19828,7 +19772,7 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>73</v>
       </c>
       <c r="B108">
@@ -19839,7 +19783,7 @@
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>52</v>
       </c>
       <c r="B109">
@@ -19850,7 +19794,7 @@
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>68</v>
       </c>
       <c r="B110">
@@ -19861,7 +19805,7 @@
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>50</v>
       </c>
       <c r="B111">
@@ -19872,7 +19816,7 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>49</v>
       </c>
       <c r="B112">
@@ -19883,7 +19827,7 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>47</v>
       </c>
       <c r="B113">
@@ -19894,7 +19838,7 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>83</v>
       </c>
       <c r="B114">
@@ -19905,7 +19849,7 @@
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>16</v>
       </c>
       <c r="B115">
